--- a/17 18 20/5.Power Bi/3) Relation/1) One to One/LeftTable.xlsx
+++ b/17 18 20/5.Power Bi/3) Relation/1) One to One/LeftTable.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>emp_id</t>
   </si>
@@ -49,13 +49,16 @@
   </si>
   <si>
     <t>Olivia</t>
+  </si>
+  <si>
+    <t>Sale</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,9 +70,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Candara"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -97,8 +105,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -381,16 +389,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="2"/>
+    <col min="4" max="4" width="4.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -400,8 +409,11 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -411,74 +423,102 @@
       <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="3">
+        <f>B2+1</f>
         <v>102</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="3">
+        <f t="shared" ref="B4:B8" si="0">B3+1</f>
         <v>103</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>7</v>
       </c>
       <c r="B5" s="3">
-        <v>107</v>
+        <f t="shared" si="0"/>
+        <v>104</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>8</v>
       </c>
       <c r="B6" s="3">
-        <v>108</v>
+        <f t="shared" si="0"/>
+        <v>105</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>9</v>
       </c>
       <c r="B7" s="3">
-        <v>109</v>
+        <f t="shared" si="0"/>
+        <v>106</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="2">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>10</v>
       </c>
       <c r="B8" s="3">
-        <v>110</v>
+        <f t="shared" si="0"/>
+        <v>107</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="D8" s="2">
+        <v>800</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>